--- a/test/E-Gadgets/Data Files/Data.xlsx
+++ b/test/E-Gadgets/Data Files/Data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4461" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4471" uniqueCount="364">
   <si>
     <t>Key</t>
   </si>
@@ -1074,6 +1074,36 @@
   </si>
   <si>
     <t>2026-05-13 02:38:08</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:42:03</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:42:32</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:43:00</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:43:28</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:43:56</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:44:24</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:44:53</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:45:21</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:45:45</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:46:10</t>
   </si>
 </sst>
 </file>
@@ -1518,7 +1548,7 @@
         <v>12</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>353</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51">

--- a/test/E-Gadgets/Data Files/Data.xlsx
+++ b/test/E-Gadgets/Data Files/Data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4471" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4536" uniqueCount="429">
   <si>
     <t>Key</t>
   </si>
@@ -1104,6 +1104,201 @@
   </si>
   <si>
     <t>2026-05-13 02:46:10</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:46:35</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:48:26</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:48:55</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:49:23</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:49:52</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:50:20</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:50:47</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:51:16</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:51:44</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:52:08</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:52:33</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:52:58</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:53:22</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:53:47</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:54:11</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:54:36</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:55:04</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:55:31</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:55:56</t>
+  </si>
+  <si>
+    <t>2026-05-13 02:56:21</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:00:45</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:01:14</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:01:42</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:02:10</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:02:38</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:03:06</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:03:33</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:04:01</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:04:25</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:04:50</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:05:15</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:05:40</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:06:05</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:06:29</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:06:54</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:07:22</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:07:50</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:08:15</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:08:39</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:15:49</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:16:19</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:16:47</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:17:15</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:20:16</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:20:46</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:21:14</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:21:42</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:22:10</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:22:38</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:23:06</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:23:34</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:23:58</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:24:23</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:24:48</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:25:13</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:25:37</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:26:02</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:26:27</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:26:54</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:27:22</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:27:47</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:28:11</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:31:52</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:38:11</t>
+  </si>
+  <si>
+    <t>2026-05-13 03:42:51</t>
   </si>
 </sst>
 </file>
@@ -1548,7 +1743,7 @@
         <v>12</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>363</v>
+        <v>428</v>
       </c>
     </row>
     <row r="51">
